--- a/fact_abastecimiento_logistica/outputs/02_configuracion_modelo.xlsx
+++ b/fact_abastecimiento_logistica/outputs/02_configuracion_modelo.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capa 1: 32 Neuronas, Capa 2: 20 Neuronas</t>
+          <t>Capa 1: 64 Neuronas, Capa 2: 32 Neuronas</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2913</v>
+        <v>10276</v>
       </c>
     </row>
     <row r="9">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>729</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="10">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.477</v>
+        <v>75.70440000000001</v>
       </c>
     </row>
     <row r="11">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64.91589999999999</v>
+        <v>78.2503</v>
       </c>
     </row>
     <row r="12">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58.8477</v>
+        <v>77.15949999999999</v>
       </c>
     </row>
     <row r="13">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.619704</v>
+        <v>0.468916</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6838880000000001</v>
+        <v>0.483028</v>
       </c>
     </row>
   </sheetData>

--- a/fact_abastecimiento_logistica/outputs/02_configuracion_modelo.xlsx
+++ b/fact_abastecimiento_logistica/outputs/02_configuracion_modelo.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capa 1: 64 Neuronas, Capa 2: 32 Neuronas</t>
+          <t>Capa 1: 32 Neuronas, Capa 2: 20 Neuronas</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75.70440000000001</v>
+        <v>75.7278</v>
       </c>
     </row>
     <row r="11">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>78.2503</v>
+        <v>77.8708</v>
       </c>
     </row>
     <row r="12">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77.15949999999999</v>
+        <v>77.3152</v>
       </c>
     </row>
     <row r="13">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.468916</v>
+        <v>0.480469</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.483028</v>
+        <v>0.49476</v>
       </c>
     </row>
   </sheetData>

--- a/fact_abastecimiento_logistica/outputs/02_configuracion_modelo.xlsx
+++ b/fact_abastecimiento_logistica/outputs/02_configuracion_modelo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/fact_abastecimiento_logistica/outputs/02_configuracion_modelo.xlsx
+++ b/fact_abastecimiento_logistica/outputs/02_configuracion_modelo.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10276</v>
+        <v>8220</v>
       </c>
     </row>
     <row r="9">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2570</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="10">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75.7278</v>
+        <v>75.4161</v>
       </c>
     </row>
     <row r="11">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77.8708</v>
+        <v>76.3869</v>
       </c>
     </row>
     <row r="12">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77.3152</v>
+        <v>78.7059</v>
       </c>
     </row>
     <row r="13">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.480469</v>
+        <v>0.460031</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.49476</v>
+        <v>0.475327</v>
       </c>
     </row>
   </sheetData>
